--- a/statistics_tables/variety_ndf_results.xlsx
+++ b/statistics_tables/variety_ndf_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">location</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t xml:space="preserve">groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSD</t>
   </si>
   <si>
     <t xml:space="preserve">mean_group_se</t>
@@ -512,19 +518,25 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>2022</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>16.0499146098425</v>
@@ -533,33 +545,39 @@
         <v>0.0524512667049356</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0000000000000000178758695250165</v>
       </c>
       <c r="I2" t="n">
+        <v>0.14581408518802</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.446229679387108</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>16.0235790061326</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0278483152369595</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="n">
         <v>2022</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>15.6187016426768</v>
@@ -568,33 +586,39 @@
         <v>0.0527101436154683</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0000000000000000178758695250165</v>
       </c>
       <c r="I3" t="n">
+        <v>0.14581408518802</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.446229679387108</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>16.0235790061326</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.0278483152369595</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>16.4021207658786</v>
@@ -603,33 +627,39 @@
         <v>0.0508179452128005</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0000000000000000178758695250165</v>
       </c>
       <c r="I4" t="n">
+        <v>0.14581408518802</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.446229679387108</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>16.0235790061326</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.0278483152369595</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>18.8395416478419</v>
@@ -638,33 +668,39 @@
         <v>0.0427795744328965</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
         <v>22</v>
       </c>
+      <c r="H5" t="n">
+        <v>0.00327145759513574</v>
+      </c>
       <c r="I5" t="n">
+        <v>0.141572162007846</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.31688651076154</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>18.7188194088675</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.0169287658500206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>18.5915204855997</v>
@@ -673,33 +709,39 @@
         <v>0.0539902230548827</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.00327145759513574</v>
       </c>
       <c r="I6" t="n">
+        <v>0.141572162007846</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.31688651076154</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>18.7188194088675</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.0169287658500206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>18.7253960931611</v>
@@ -708,33 +750,39 @@
         <v>0.0538684709242255</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.00327145759513574</v>
       </c>
       <c r="I7" t="n">
+        <v>0.141572162007846</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.31688651076154</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>18.7188194088675</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0169287658500206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" t="n">
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>16.0432461254442</v>
@@ -743,33 +791,39 @@
         <v>0.0387862993111708</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.00000000000000000000000909301286899114</v>
       </c>
       <c r="I8" t="n">
+        <v>0.106380358147486</v>
+      </c>
+      <c r="J8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.373730966283321</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>15.994105531341</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0233667938198221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" t="n">
         <v>2022</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>15.6087001382237</v>
@@ -778,33 +832,39 @@
         <v>0.0381186827996416</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>28</v>
+        <v>19</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00000000000000000000000909301286899114</v>
       </c>
       <c r="I9" t="n">
+        <v>0.106380358147486</v>
+      </c>
+      <c r="J9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.373730966283321</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>15.994105531341</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.0233667938198221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" t="n">
         <v>2022</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>16.3303703303551</v>
@@ -813,33 +873,39 @@
         <v>0.0368817159943348</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00000000000000000000000909301286899114</v>
       </c>
       <c r="I10" t="n">
+        <v>0.106380358147486</v>
+      </c>
+      <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.373730966283321</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>15.994105531341</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.0233667938198221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>16.34834825348</v>
@@ -848,33 +914,39 @@
         <v>0.0478343019784456</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.000000000000000000177968835431363</v>
       </c>
       <c r="I11" t="n">
+        <v>0.147314231227816</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.471052826492426</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>16.2198476434771</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.0290417540809554</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>15.740296533872</v>
@@ -883,33 +955,39 @@
         <v>0.0546024593518098</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.000000000000000000177968835431363</v>
       </c>
       <c r="I12" t="n">
+        <v>0.147314231227816</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.471052826492426</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>16.2198476434771</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.0290417540809554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>16.5708981430793</v>
@@ -918,33 +996,39 @@
         <v>0.0548651128931226</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" t="s">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.000000000000000000177968835431363</v>
       </c>
       <c r="I13" t="n">
+        <v>0.147314231227816</v>
+      </c>
+      <c r="J13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.471052826492426</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>16.2198476434771</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.0290417540809554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>14.912101680041</v>
@@ -953,33 +1037,39 @@
         <v>0.0620308900279665</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>33</v>
+        <v>16</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0000000913497196791692</v>
       </c>
       <c r="I14" t="n">
+        <v>0.211057423800995</v>
+      </c>
+      <c r="J14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" t="n">
         <v>0.522033380390639</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>15.1205472451957</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.0345247676506224</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B15" t="n">
         <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>14.9509289444349</v>
@@ -988,33 +1078,39 @@
         <v>0.0818183211010285</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>34</v>
+        <v>16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0000000913497196791692</v>
       </c>
       <c r="I15" t="n">
+        <v>0.211057423800995</v>
+      </c>
+      <c r="J15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.522033380390639</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>15.1205472451957</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.0345247676506224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B16" t="n">
         <v>2024</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>15.4986111111111</v>
@@ -1023,33 +1119,39 @@
         <v>0.0803318047451663</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" t="s">
-        <v>35</v>
+        <v>22</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0000000913497196791692</v>
       </c>
       <c r="I16" t="n">
+        <v>0.211057423800995</v>
+      </c>
+      <c r="J16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.522033380390639</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>15.1205472451957</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0345247676506224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" t="n">
         <v>2022</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>16.8275730701552</v>
@@ -1058,33 +1160,39 @@
         <v>0.0434918466102381</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>37</v>
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0000000000000000000000000000147043107298813</v>
       </c>
       <c r="I17" t="n">
+        <v>0.115311735674744</v>
+      </c>
+      <c r="J17" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.459966319165705</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>16.9719042407975</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0271016329481771</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B18" t="n">
         <v>2022</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>16.585799023668</v>
@@ -1093,33 +1201,39 @@
         <v>0.0297497239849342</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" t="s">
-        <v>38</v>
+        <v>19</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0000000000000000000000000000147043107298813</v>
       </c>
       <c r="I18" t="n">
+        <v>0.115311735674744</v>
+      </c>
+      <c r="J18" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.459966319165705</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>16.9719042407975</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.0271016329481771</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B19" t="n">
         <v>2022</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>17.5023406285692</v>
@@ -1128,33 +1242,39 @@
         <v>0.0479219908606275</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" t="s">
-        <v>39</v>
+        <v>22</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0000000000000000000000000000147043107298813</v>
       </c>
       <c r="I19" t="n">
+        <v>0.115311735674744</v>
+      </c>
+      <c r="J19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.459966319165705</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>16.9719042407975</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.0271016329481771</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>19.5915927788524</v>
@@ -1163,33 +1283,39 @@
         <v>0.0311263963798103</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.00000000000000000000217549025012775</v>
       </c>
       <c r="I20" t="n">
+        <v>0.0948741462682035</v>
+      </c>
+      <c r="J20" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.316366003685905</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>19.5216673135554</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.0162058905422606</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>19.1951984636563</v>
@@ -1198,33 +1324,39 @@
         <v>0.0348555876268675</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.00000000000000000000217549025012775</v>
       </c>
       <c r="I21" t="n">
+        <v>0.0948741462682035</v>
+      </c>
+      <c r="J21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.316366003685905</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>19.5216673135554</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.0162058905422606</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
         <v>19.7782106981574</v>
@@ -1233,33 +1365,39 @@
         <v>0.03536115310779</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" t="s">
-        <v>42</v>
+        <v>22</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.00000000000000000000217549025012775</v>
       </c>
       <c r="I22" t="n">
+        <v>0.0948741462682035</v>
+      </c>
+      <c r="J22" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.316366003685905</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>19.5216673135554</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.0162058905422606</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B23" t="n">
         <v>2024</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>16.9083333333333</v>
@@ -1268,33 +1406,37 @@
         <v>0.0647871974419403</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" t="n">
+        <v>22</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.851729686640396</v>
+      </c>
+      <c r="I23"/>
+      <c r="J23" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.331403904534126</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>16.8943518518519</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.0196162544405513</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="n">
         <v>2024</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>16.8686111111111</v>
@@ -1303,33 +1445,37 @@
         <v>0.051049544527573</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.851729686640396</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.331403904534126</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>16.8943518518519</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.0196162544405513</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B25" t="n">
         <v>2024</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>16.9061111111111</v>
@@ -1338,18 +1484,22 @@
         <v>0.0499480329589932</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" t="n">
+        <v>22</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.851729686640396</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25" t="s">
+        <v>47</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.331403904534126</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>16.8943518518519</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0196162544405513</v>
       </c>
     </row>
